--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486955_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486955_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.5381</v>
+        <v>9.2051</v>
       </c>
       <c r="E2" t="n">
-        <v>8.851599999999999</v>
+        <v>9.192500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3135</v>
+        <v>0.0126</v>
       </c>
       <c r="G2" t="n">
         <v>8.992599999999999</v>
@@ -610,13 +610,13 @@
         <v>1.0267</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0307</v>
+        <v>0.6364</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4147</v>
+        <v>-0.0738</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3841</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>0.6028</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5869</v>
+        <v>2.2437</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0588</v>
+        <v>4.2491</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4719</v>
+        <v>-2.0055</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2456</v>
@@ -688,13 +688,13 @@
         <v>1.2321</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8057</v>
+        <v>1.4625</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4874</v>
+        <v>0.6777</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3183</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>P. SUÁREZ CUSTODIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3797</v>
+        <v>0.9857</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0061</v>
+        <v>3.3538</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6264</v>
+        <v>-2.3682</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5355</v>
+        <v>1.6807</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4539</v>
+        <v>-1.2394</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08160000000000001</v>
+        <v>2.9201</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8981</v>
+        <v>3.0242</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7008</v>
+        <v>-0.3825</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1973</v>
+        <v>3.4067</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3626</v>
+        <v>-1.3435</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2468</v>
+        <v>-0.8569</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1157</v>
+        <v>-0.4866</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6121</v>
+        <v>0.2605</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0731</v>
+        <v>-0.2597</v>
       </c>
       <c r="U4" t="n">
-        <v>0.539</v>
+        <v>0.5203</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.1786</v>
+        <v>-1.777</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2402</v>
+        <v>0.5893</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4189</v>
+        <v>-2.3663</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. SUÁREZ CUSTODIO</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4923</v>
+        <v>0.7817</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8308</v>
+        <v>1.3784</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3385</v>
+        <v>-0.5967</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6807</v>
+        <v>0.5355</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2394</v>
+        <v>0.4539</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9201</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0242</v>
+        <v>0.8981</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3825</v>
+        <v>0.7008</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4067</v>
+        <v>0.1973</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3435</v>
+        <v>-0.3626</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8569</v>
+        <v>-0.2468</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4866</v>
+        <v>-0.1157</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2328</v>
+        <v>1.0141</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7827</v>
+        <v>0.4455</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5687</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.777</v>
+        <v>-1.1786</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5893</v>
+        <v>0.2402</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3663</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0701</v>
+        <v>0.3665</v>
       </c>
       <c r="E6" t="n">
         <v>1.5816</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5115</v>
+        <v>-1.2151</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6899999999999999</v>
@@ -922,13 +922,13 @@
         <v>0.616</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0427</v>
+        <v>0.2537</v>
       </c>
       <c r="T6" t="n">
         <v>0.1781</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2208</v>
+        <v>0.0756</v>
       </c>
       <c r="V6" t="n">
         <v>1.4189</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.963</v>
+        <v>-0.9063</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3522</v>
+        <v>-0.3251</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6108</v>
+        <v>-0.5812</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1706</v>
@@ -1000,13 +1000,13 @@
         <v>1.0267</v>
       </c>
       <c r="S7" t="n">
-        <v>0.504</v>
+        <v>0.5608</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0854</v>
+        <v>-0.0582</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5894</v>
+        <v>0.6191</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2965</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7631</v>
+        <v>-2.6115</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5561</v>
+        <v>-2.1377</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.207</v>
+        <v>-0.4738</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9922</v>
@@ -1078,13 +1078,13 @@
         <v>0.4107</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3182</v>
+        <v>0.4698</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6587</v>
+        <v>-0.2403</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9769</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0.5803</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3683</v>
+        <v>-3.0866</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7924</v>
+        <v>-1.4515</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5759</v>
+        <v>-1.6352</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3129</v>
@@ -1156,13 +1156,13 @@
         <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3634</v>
+        <v>0.6451</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.283</v>
+        <v>0.0579</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6464</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4189</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5167</v>
+        <v>-4.1296</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1066</v>
+        <v>-2.8974</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4101</v>
+        <v>-1.2322</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8491</v>
@@ -1234,13 +1234,13 @@
         <v>0.616</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8114</v>
+        <v>-0.4243</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.651</v>
+        <v>-0.4418</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1604</v>
+        <v>0.0175</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2402</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5673</v>
+        <v>-4.447</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8114</v>
+        <v>-3.6022</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7559</v>
+        <v>-0.8448</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4778</v>
@@ -1312,13 +1312,13 @@
         <v>0.2053</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0011</v>
+        <v>0.1191</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4611</v>
+        <v>-0.2519</v>
       </c>
       <c r="U11" t="n">
-        <v>0.46</v>
+        <v>0.371</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2402</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.2471</v>
+        <v>-6.1013</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9086</v>
+        <v>-5.8815</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3385</v>
+        <v>-0.2199</v>
       </c>
       <c r="G12" t="n">
         <v>-3.7972</v>
@@ -1390,13 +1390,13 @@
         <v>0.616</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3847</v>
+        <v>1.5304</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8096</v>
+        <v>0.8367</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.6937</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1651</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.3584</v>
+        <v>-7.699599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.801600000000001</v>
+        <v>3.46</v>
       </c>
       <c r="F13" t="n">
         <v>-11.16</v>
@@ -1468,13 +1468,13 @@
         <v>8.2136</v>
       </c>
       <c r="S13" t="n">
-        <v>5.869400000000001</v>
+        <v>6.528100000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2115999999999999</v>
+        <v>0.8702000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>5.6579</v>
+        <v>5.658300000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-4.7145</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4138</v>
+        <v>6.3527</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9195</v>
+        <v>5.0241</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4943</v>
+        <v>1.3286</v>
       </c>
       <c r="G14" t="n">
         <v>-0.6666</v>
@@ -1546,13 +1546,13 @@
         <v>2.6694</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6876</v>
+        <v>-0.7487</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0153</v>
+        <v>-0.9107</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3277</v>
+        <v>0.162</v>
       </c>
       <c r="V14" t="n">
         <v>5.3038</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9656</v>
+        <v>2.9858</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7181</v>
+        <v>2.0445</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2474</v>
+        <v>0.9414</v>
       </c>
       <c r="G15" t="n">
         <v>2.7395</v>
@@ -1624,13 +1624,13 @@
         <v>1.0267</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5628</v>
+        <v>0.5831</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8013</v>
+        <v>0.1277</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2385</v>
+        <v>0.4554</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1314</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. MERLO</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.534</v>
+        <v>1.584</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4878</v>
+        <v>0.5818</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0462</v>
+        <v>1.0021</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9701</v>
+        <v>2.1666</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5614</v>
+        <v>1.9402</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.5913</v>
+        <v>0.2264</v>
       </c>
       <c r="J16" t="n">
-        <v>4.4975</v>
+        <v>3.5997</v>
       </c>
       <c r="K16" t="n">
-        <v>5.1424</v>
+        <v>1.1003</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6449</v>
+        <v>2.4994</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5275</v>
+        <v>-1.4331</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.581</v>
+        <v>0.8398</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9465</v>
+        <v>-2.2729</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.4374</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.2855</v>
+        <v>-3.0801</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8481</v>
+        <v>2.2588</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4175</v>
+        <v>-0.5908</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3833</v>
+        <v>-0.7673</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9658</v>
+        <v>0.1765</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4189</v>
+        <v>0.8295</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6591</v>
+        <v>0.8295</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>J. GONZALEZ ALBADALEJO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0645</v>
+        <v>1.5243</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1634</v>
+        <v>-0.2934</v>
       </c>
       <c r="F17" t="n">
-        <v>0.901</v>
+        <v>1.8177</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1666</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9402</v>
+        <v>-2.2416</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2264</v>
+        <v>2.3338</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5997</v>
+        <v>0.0357</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1003</v>
+        <v>-2.1081</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4994</v>
+        <v>2.1438</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4331</v>
+        <v>0.0566</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8398</v>
+        <v>-0.1335</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.2729</v>
+        <v>0.19</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0801</v>
+        <v>-0.2053</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2588</v>
+        <v>1.6427</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1103</v>
+        <v>-0.5947</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1857</v>
+        <v>-0.9533</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.3586</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8295</v>
+        <v>0.5893</v>
       </c>
       <c r="W17" t="n">
         <v>0.8295</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. GONZALEZ ALBADALEJO</t>
+          <t>S. MERLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4608</v>
+        <v>1.4189</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.921</v>
+        <v>1.9063</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3818</v>
+        <v>-0.4874</v>
       </c>
       <c r="G18" t="n">
-        <v>0.09229999999999999</v>
+        <v>1.9701</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.2416</v>
+        <v>4.5614</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3338</v>
+        <v>-2.5913</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0357</v>
+        <v>4.4975</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.1081</v>
+        <v>5.1424</v>
       </c>
       <c r="L18" t="n">
-        <v>2.1438</v>
+        <v>-0.6449</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0566</v>
+        <v>-2.5275</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1335</v>
+        <v>-0.581</v>
       </c>
       <c r="O18" t="n">
-        <v>0.19</v>
+        <v>-1.9465</v>
       </c>
       <c r="P18" t="n">
-        <v>1.4374</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2053</v>
+        <v>-3.2855</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6582</v>
+        <v>-0.5327</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.5809</v>
+        <v>-0.9649</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.4322</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5893</v>
+        <v>1.4189</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8295</v>
+        <v>1.6591</v>
       </c>
       <c r="X18" t="n">
         <v>-0.2402</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0232</v>
+        <v>0.2359</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1574</v>
+        <v>2.0528</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1342</v>
+        <v>-1.8169</v>
       </c>
       <c r="G19" t="n">
         <v>0.3782</v>
@@ -1936,13 +1936,13 @@
         <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8191000000000001</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2907</v>
+        <v>-0.3953</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5284</v>
+        <v>-0.211</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1786</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0039</v>
+        <v>-0.2246</v>
       </c>
       <c r="E20" t="n">
-        <v>1.711</v>
+        <v>2.0248</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7149</v>
+        <v>-2.2494</v>
       </c>
       <c r="G20" t="n">
         <v>1.8803</v>
@@ -2014,13 +2014,13 @@
         <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4099</v>
+        <v>-0.6306</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7905</v>
+        <v>-0.4767</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6194</v>
+        <v>-0.1539</v>
       </c>
       <c r="V20" t="n">
         <v>-2.7063</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9256</v>
+        <v>-2.0006</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.8692</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.161</v>
+        <v>-1.1313</v>
       </c>
       <c r="G21" t="n">
         <v>-3.3715</v>
@@ -2092,13 +2092,13 @@
         <v>1.4374</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5808</v>
+        <v>-0.6558</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4225</v>
+        <v>-0.5271</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1583</v>
+        <v>-0.1287</v>
       </c>
       <c r="V21" t="n">
         <v>0.5893</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1738</v>
+        <v>-2.1233</v>
       </c>
       <c r="E22" t="n">
         <v>-1.3116</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8622</v>
+        <v>-0.8117</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8623</v>
@@ -2170,13 +2170,13 @@
         <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7489</v>
+        <v>-0.6984</v>
       </c>
       <c r="T22" t="n">
         <v>-0.7905</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0416</v>
+        <v>0.0921</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>8.358599999999999</v>
+        <v>9.7531</v>
       </c>
       <c r="E23" t="n">
-        <v>11.16</v>
+        <v>11.1601</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8016</v>
+        <v>-1.4069</v>
       </c>
       <c r="G23" t="n">
         <v>2.3266</v>
@@ -2218,7 +2218,7 @@
         <v>9.166</v>
       </c>
       <c r="I23" t="n">
-        <v>-6.839599999999999</v>
+        <v>-6.8396</v>
       </c>
       <c r="J23" t="n">
         <v>14.619</v>
@@ -2248,13 +2248,13 @@
         <v>15.4007</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.869499999999999</v>
+        <v>-4.475000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-5.6581</v>
+        <v>-5.658099999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2114000000000001</v>
+        <v>1.1832</v>
       </c>
       <c r="V23" t="n">
         <v>4.714499999999999</v>
